--- a/site/Papaya-Global-Workday-Integraiton-Guide/headings.xlsx
+++ b/site/Papaya-Global-Workday-Integraiton-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,204 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01KXFPYQE5QHRBRECWZ49E5AV4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFPYQE5QHRBRECWZ49E5AV4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KXFQQQZSTP3G14T0DJMEGS60</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFQQQZSTP3G14T0DJMEGS60</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Application Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KXFQTAST0ZK34TP6H0VBVG8G</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFQTAST0ZK34TP6H0VBVG8G</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SFTP Configuration</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KXFR44N8PYZ6267K2DE4Y58N</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFR44N8PYZ6267K2DE4Y58N</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SFTP sync settings</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KXFRA5PXX0D5BH68MK5VPJVQ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFRA5PXX0D5BH68MK5VPJVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Worker sync configuration</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KXFTD3P5WPHRSH3SB5TETVJM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFTD3P5WPHRSH3SB5TETVJM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>How to obtain the file path</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KXFW9EBSTSMRZTB1E1D9P8PZ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Papaya-Global-Workday-Integraiton-Guide/#h_01KXFW9EBSTSMRZTB1E1D9P8PZ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
